--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -567,7 +567,7 @@
         <v>46099</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -591,7 +591,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -591,7 +591,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -591,7 +591,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -591,7 +591,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -591,7 +591,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -591,7 +591,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -542,30 +542,35 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>Geotifflänk</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>Knärotsbuffertlänk</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Klagomålslänk</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Klagomålsmaillänk</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Tillsynsbegäranslänk</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Tillsynsbegäransmaillänk</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
         </is>
@@ -591,7 +596,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -662,23 +667,27 @@
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/kartor/S 215-2024 karta.png", "S 215-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0481/kartor_geotiff/S 215-2024 georefererad karta.tif", "S 215-2024")</f>
+        <v/>
+      </c>
+      <c r="Z2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/klagomål/S 215-2024 FSC-klagomål.docx", "S 215-2024")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/klagomålsmail/S 215-2024 FSC-klagomål mail.docx", "S 215-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/tillsyn/S 215-2024 tillsynsbegäran.docx", "S 215-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/tillsynsmail/S 215-2024 tillsynsbegäran mail.docx", "S 215-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/fåglar/S 215-2024 prioriterade fågelarter.docx", "S 215-2024")</f>
         <v/>
       </c>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AE2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -522,55 +522,60 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Antal fynd</t>
+          <t>Fynd</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Nya fynd</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>Artnamn</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Artfyndslänk</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Kartlänk</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Geotifflänk</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Knärotsbuffertlänk</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Klagomålslänk</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Klagomålsmaillänk</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Tillsynsbegäranslänk</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Tillsynsbegäransmaillänk</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Fågeltillsynsbegäranslänk</t>
         </is>
@@ -596,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -649,7 +654,10 @@
       <c r="T2" t="n">
         <v>8</v>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Björktrast
 Korallticka
@@ -659,35 +667,35 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="V2">
+      <c r="W2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/artfynd/S 215-2024 artfynd.xlsx", "S 215-2024")</f>
         <v/>
       </c>
-      <c r="W2">
+      <c r="X2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/kartor/S 215-2024 karta.png", "S 215-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="Y2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/kartor_geotiff/S 215-2024 georefererad karta.tif", "S 215-2024")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/klagomål/S 215-2024 FSC-klagomål.docx", "S 215-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/klagomålsmail/S 215-2024 FSC-klagomål mail.docx", "S 215-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/tillsyn/S 215-2024 tillsynsbegäran.docx", "S 215-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/tillsynsmail/S 215-2024 tillsynsbegäran mail.docx", "S 215-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AE2">
         <f>HYPERLINK("https://klasma.github.io/Logging_0481/fåglar/S 215-2024 prioriterade fågelarter.docx", "S 215-2024")</f>
         <v/>
       </c>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/Översikt OXELÖSUND.xlsx
+++ b/Översikt OXELÖSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
